--- a/data_lake/datos_diarios_preliminares/dt=2026-07-23/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-23/Temp-max-julio-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAA1DAB-7C34-475F-82BE-558340007586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C1012F-4726-49C1-B0A2-152DD34EE689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMAX_PRINCIPALES_CIUDADES" sheetId="1" r:id="rId1"/>
@@ -9487,7 +9487,9 @@
       <c r="Y5" s="57">
         <v>30.8</v>
       </c>
-      <c r="Z5" s="57"/>
+      <c r="Z5" s="57">
+        <v>30.7</v>
+      </c>
       <c r="AA5" s="57"/>
       <c r="AB5" s="57"/>
       <c r="AC5" s="57"/>
@@ -9499,7 +9501,7 @@
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9517,11 +9519,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.076190476190476</v>
+        <v>31.059090909090912</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.87881870018224717</v>
+        <v>0.86171913308268344</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9600,7 +9602,9 @@
       <c r="Y6" s="57">
         <v>30.8</v>
       </c>
-      <c r="Z6" s="57"/>
+      <c r="Z6" s="57">
+        <v>31.1</v>
+      </c>
       <c r="AA6" s="57"/>
       <c r="AB6" s="57"/>
       <c r="AC6" s="57"/>
@@ -9612,7 +9616,7 @@
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9630,11 +9634,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.62380952380952</v>
+        <v>30.645454545454541</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-3.0470873212820493E-2</v>
+        <v>-8.8258515677992477E-3</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9713,7 +9717,9 @@
       <c r="Y7" s="57">
         <v>32.6</v>
       </c>
-      <c r="Z7" s="57"/>
+      <c r="Z7" s="57">
+        <v>35</v>
+      </c>
       <c r="AA7" s="57"/>
       <c r="AB7" s="57"/>
       <c r="AC7" s="57"/>
@@ -9725,7 +9731,7 @@
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>35</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9743,11 +9749,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.733333333333334</v>
+        <v>35.699999999999996</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>2.3673173257642617</v>
+        <v>2.3339839924309231</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9826,7 +9832,9 @@
       <c r="Y8" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="Z8" s="57"/>
+      <c r="Z8" s="57">
+        <v>33.1</v>
+      </c>
       <c r="AA8" s="57"/>
       <c r="AB8" s="57"/>
       <c r="AC8" s="57"/>
@@ -9838,7 +9846,7 @@
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>33.1</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9856,11 +9864,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.247619047619047</v>
+        <v>33.240909090909092</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>0.99857603686635343</v>
+        <v>0.99186608015639877</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9939,7 +9947,9 @@
       <c r="Y9" s="57">
         <v>34</v>
       </c>
-      <c r="Z9" s="57"/>
+      <c r="Z9" s="57">
+        <v>33.6</v>
+      </c>
       <c r="AA9" s="57"/>
       <c r="AB9" s="57"/>
       <c r="AC9" s="57"/>
@@ -9951,7 +9961,7 @@
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -9969,11 +9979,11 @@
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>33.785714285714285</v>
+        <v>33.777272727272731</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.69446814803043821</v>
+        <v>0.68602658958888441</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10052,7 +10062,9 @@
       <c r="Y10" s="57">
         <v>35.799999999999997</v>
       </c>
-      <c r="Z10" s="57"/>
+      <c r="Z10" s="57">
+        <v>35.5</v>
+      </c>
       <c r="AA10" s="57"/>
       <c r="AB10" s="57"/>
       <c r="AC10" s="57"/>
@@ -10064,7 +10076,7 @@
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>35.799999999999997</v>
+        <v>35.5</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -10082,11 +10094,11 @@
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.785714285714278</v>
+        <v>35.772727272727266</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.40547605805392095</v>
+        <v>0.39248904506690963</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10165,7 +10177,9 @@
       <c r="Y11" s="57">
         <v>37.4</v>
       </c>
-      <c r="Z11" s="57"/>
+      <c r="Z11" s="57">
+        <v>37.700000000000003</v>
+      </c>
       <c r="AA11" s="57"/>
       <c r="AB11" s="57"/>
       <c r="AC11" s="57"/>
@@ -10177,7 +10191,7 @@
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>37.4</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
@@ -10195,11 +10209,11 @@
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.147619047619038</v>
+        <v>38.127272727272718</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.6103349547704369</v>
+        <v>2.5899886344241168</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10278,7 +10292,9 @@
       <c r="Y12" s="57">
         <v>33.4</v>
       </c>
-      <c r="Z12" s="57"/>
+      <c r="Z12" s="57">
+        <v>34.200000000000003</v>
+      </c>
       <c r="AA12" s="57"/>
       <c r="AB12" s="57"/>
       <c r="AC12" s="57"/>
@@ -10290,7 +10306,7 @@
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10308,11 +10324,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.67619047619047</v>
+        <v>34.654545454545456</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.4875663300167332</v>
+        <v>2.4659213083717191</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10391,7 +10407,9 @@
       <c r="Y13" s="57">
         <v>33.799999999999997</v>
       </c>
-      <c r="Z13" s="57"/>
+      <c r="Z13" s="57">
+        <v>35</v>
+      </c>
       <c r="AA13" s="57"/>
       <c r="AB13" s="57"/>
       <c r="AC13" s="57"/>
@@ -10403,7 +10421,7 @@
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <v>35</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10421,11 +10439,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.857142857142854</v>
+        <v>35.81818181818182</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>2.4753507424475174</v>
+        <v>2.4363897034864834</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10504,7 +10522,9 @@
       <c r="Y14" s="57">
         <v>34.9</v>
       </c>
-      <c r="Z14" s="57"/>
+      <c r="Z14" s="57">
+        <v>35.9</v>
+      </c>
       <c r="AA14" s="57"/>
       <c r="AB14" s="57"/>
       <c r="AC14" s="57"/>
@@ -10516,7 +10536,7 @@
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>34.9</v>
+        <v>35.9</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10534,11 +10554,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>35.042857142857144</v>
+        <v>35.081818181818178</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.8179205436429129</v>
+        <v>1.8568815826039469</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10617,7 +10637,9 @@
       <c r="Y15" s="57">
         <v>31.9</v>
       </c>
-      <c r="Z15" s="57"/>
+      <c r="Z15" s="57">
+        <v>32.799999999999997</v>
+      </c>
       <c r="AA15" s="57"/>
       <c r="AB15" s="57"/>
       <c r="AC15" s="57"/>
@@ -10629,7 +10651,7 @@
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>31.9</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10647,11 +10669,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.823809523809523</v>
+        <v>31.868181818181814</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>8.8472067729572501E-2</v>
+        <v>0.13284436210186357</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10779,7 +10801,9 @@
       <c r="Y17" s="57">
         <v>31.6</v>
       </c>
-      <c r="Z17" s="57"/>
+      <c r="Z17" s="57">
+        <v>34.4</v>
+      </c>
       <c r="AA17" s="57"/>
       <c r="AB17" s="57"/>
       <c r="AC17" s="57"/>
@@ -10791,7 +10815,7 @@
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>31.6</v>
+        <v>34.4</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10809,11 +10833,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.304761904761897</v>
+        <v>34.309090909090905</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.6307797023147401</v>
+        <v>1.6351087066437486</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10892,7 +10916,9 @@
       <c r="Y18" s="57">
         <v>25.9</v>
       </c>
-      <c r="Z18" s="57"/>
+      <c r="Z18" s="57">
+        <v>28.6</v>
+      </c>
       <c r="AA18" s="57"/>
       <c r="AB18" s="57"/>
       <c r="AC18" s="57"/>
@@ -10904,7 +10930,7 @@
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>25.9</v>
+        <v>28.6</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -10922,11 +10948,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.871428571428574</v>
+        <v>27.90454545454546</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.8115577174717039</v>
+        <v>1.8446746005885899</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11005,7 +11031,9 @@
       <c r="Y19" s="57">
         <v>33.700000000000003</v>
       </c>
-      <c r="Z19" s="57"/>
+      <c r="Z19" s="57">
+        <v>36.4</v>
+      </c>
       <c r="AA19" s="57"/>
       <c r="AB19" s="57"/>
       <c r="AC19" s="57"/>
@@ -11017,7 +11045,7 @@
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>33.700000000000003</v>
+        <v>36.4</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -11035,11 +11063,11 @@
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>33.590476190476188</v>
+        <v>33.718181818181819</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.33951378780654551</v>
+        <v>0.46721941551217583</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11118,7 +11146,9 @@
       <c r="Y20" s="57">
         <v>31.2</v>
       </c>
-      <c r="Z20" s="57"/>
+      <c r="Z20" s="57">
+        <v>28.6</v>
+      </c>
       <c r="AA20" s="57"/>
       <c r="AB20" s="57"/>
       <c r="AC20" s="57"/>
@@ -11130,7 +11160,7 @@
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -11148,11 +11178,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.423809523809528</v>
+        <v>30.340909090909097</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.7830049261083794</v>
+        <v>1.7001044932079488</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11231,7 +11261,9 @@
       <c r="Y21" s="57">
         <v>24.4</v>
       </c>
-      <c r="Z21" s="57"/>
+      <c r="Z21" s="57">
+        <v>25.3</v>
+      </c>
       <c r="AA21" s="57"/>
       <c r="AB21" s="57"/>
       <c r="AC21" s="57"/>
@@ -11243,7 +11275,7 @@
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>24.4</v>
+        <v>25.3</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11261,11 +11293,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.295238095238091</v>
+        <v>24.340909090909086</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.6857349435881197</v>
+        <v>1.7314059392591155</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11412,7 +11444,9 @@
       <c r="Y23" s="57">
         <v>29.2</v>
       </c>
-      <c r="Z23" s="57"/>
+      <c r="Z23" s="57">
+        <v>29.9</v>
+      </c>
       <c r="AA23" s="57"/>
       <c r="AB23" s="57"/>
       <c r="AC23" s="57"/>
@@ -11424,7 +11458,7 @@
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>29.2</v>
+        <v>29.9</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11442,11 +11476,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.671428571428578</v>
+        <v>28.727272727272734</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.8030414746543784</v>
+        <v>1.8588856304985342</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11525,7 +11559,9 @@
       <c r="Y24" s="57">
         <v>28.5</v>
       </c>
-      <c r="Z24" s="57"/>
+      <c r="Z24" s="57">
+        <v>29.8</v>
+      </c>
       <c r="AA24" s="57"/>
       <c r="AB24" s="57"/>
       <c r="AC24" s="57"/>
@@ -11537,7 +11573,7 @@
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>29.8</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11555,11 +11591,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.62857142857143</v>
+        <v>29.636363636363637</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.3767473118279483</v>
+        <v>1.3845395196201551</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11638,7 +11674,9 @@
       <c r="Y25" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="Z25" s="57"/>
+      <c r="Z25" s="57">
+        <v>34.1</v>
+      </c>
       <c r="AA25" s="57"/>
       <c r="AB25" s="57"/>
       <c r="AC25" s="57"/>
@@ -11650,7 +11688,7 @@
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>34.1</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -11668,11 +11706,11 @@
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.280952380952385</v>
+        <v>32.363636363636367</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>1.9050869877313161</v>
+        <v>1.9877709704152977</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11751,7 +11789,9 @@
       <c r="Y26" s="57">
         <v>20.3</v>
       </c>
-      <c r="Z26" s="57"/>
+      <c r="Z26" s="57">
+        <v>20.7</v>
+      </c>
       <c r="AA26" s="57"/>
       <c r="AB26" s="57"/>
       <c r="AC26" s="57"/>
@@ -11763,7 +11803,7 @@
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -11781,11 +11821,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.680952380952384</v>
+        <v>19.72727272727273</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.1380807735090244</v>
+        <v>1.1844011198293707</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11864,7 +11904,9 @@
       <c r="Y27" s="57">
         <v>19.600000000000001</v>
       </c>
-      <c r="Z27" s="57"/>
+      <c r="Z27" s="57">
+        <v>21.2</v>
+      </c>
       <c r="AA27" s="57"/>
       <c r="AB27" s="57"/>
       <c r="AC27" s="57"/>
@@ -11876,7 +11918,7 @@
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>19.600000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -11894,11 +11936,11 @@
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>18.719047619047618</v>
+        <v>18.831818181818178</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>2.0369970749392294</v>
+        <v>2.1497676377097896</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11977,7 +12019,9 @@
       <c r="Y28" s="57">
         <v>32.1</v>
       </c>
-      <c r="Z28" s="57"/>
+      <c r="Z28" s="57">
+        <v>33.6</v>
+      </c>
       <c r="AA28" s="57"/>
       <c r="AB28" s="57"/>
       <c r="AC28" s="57"/>
@@ -11989,7 +12033,7 @@
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>32.1</v>
+        <v>33.6</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -12007,11 +12051,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>31.904761904761909</v>
+        <v>31.981818181818188</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.3763093031057494</v>
+        <v>1.4533655801620284</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12156,7 +12200,9 @@
       <c r="Y30" s="57">
         <v>36.5</v>
       </c>
-      <c r="Z30" s="57"/>
+      <c r="Z30" s="57">
+        <v>36</v>
+      </c>
       <c r="AA30" s="57"/>
       <c r="AB30" s="57"/>
       <c r="AC30" s="57"/>
@@ -12168,7 +12214,7 @@
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12186,11 +12232,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>34.63333333333334</v>
+        <v>34.695454545454545</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>0.89108243727599046</v>
+        <v>0.95320364939719582</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12269,7 +12315,9 @@
       <c r="Y31" s="57">
         <v>24.9</v>
       </c>
-      <c r="Z31" s="57"/>
+      <c r="Z31" s="57">
+        <v>29.1</v>
+      </c>
       <c r="AA31" s="57"/>
       <c r="AB31" s="57"/>
       <c r="AC31" s="57"/>
@@ -12281,7 +12329,7 @@
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>24.9</v>
+        <v>29.1</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -12299,11 +12347,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.290476190476188</v>
+        <v>27.372727272727271</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>1.9030513533555684</v>
+        <v>1.985302435606652</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12382,7 +12430,9 @@
       <c r="Y32" s="57">
         <v>19.600000000000001</v>
       </c>
-      <c r="Z32" s="57"/>
+      <c r="Z32" s="57">
+        <v>20</v>
+      </c>
       <c r="AA32" s="57"/>
       <c r="AB32" s="57"/>
       <c r="AC32" s="57"/>
@@ -12394,7 +12444,7 @@
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>19.600000000000001</v>
+        <v>20</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12412,11 +12462,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>18.019047619047619</v>
+        <v>18.109090909090909</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.6895098457863682</v>
+        <v>1.7795531358296586</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12495,7 +12545,9 @@
       <c r="Y33" s="57">
         <v>16.600000000000001</v>
       </c>
-      <c r="Z33" s="57"/>
+      <c r="Z33" s="57">
+        <v>16.399999999999999</v>
+      </c>
       <c r="AA33" s="57"/>
       <c r="AB33" s="57"/>
       <c r="AC33" s="57"/>
@@ -12507,7 +12559,7 @@
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>16.600000000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12525,11 +12577,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.795238095238094</v>
+        <v>15.822727272727271</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>1.0506255627946448</v>
+        <v>1.0781147402838211</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -12660,7 +12712,9 @@
       <c r="Y35" s="57">
         <v>31.2</v>
       </c>
-      <c r="Z35" s="57"/>
+      <c r="Z35" s="57">
+        <v>31</v>
+      </c>
       <c r="AA35" s="57"/>
       <c r="AB35" s="57"/>
       <c r="AC35" s="57"/>
@@ -12672,7 +12726,7 @@
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -12690,11 +12744,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>31.952380952380945</v>
+        <v>31.909090909090903</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.87968509984638388</v>
+        <v>0.83639505655634139</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -12894,7 +12948,9 @@
       <c r="Y38" s="57">
         <v>31.6</v>
       </c>
-      <c r="Z38" s="57"/>
+      <c r="Z38" s="57">
+        <v>29</v>
+      </c>
       <c r="AA38" s="57"/>
       <c r="AB38" s="57"/>
       <c r="AC38" s="57"/>
@@ -12906,7 +12962,7 @@
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>31.6</v>
+        <v>29</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -12924,11 +12980,11 @@
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.119047619047613</v>
+        <v>30.068181818181813</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>9.0021395655032421E-2</v>
+        <v>3.915559478923214E-2</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -13008,7 +13064,9 @@
       <c r="Y39" s="57">
         <v>33.1</v>
       </c>
-      <c r="Z39" s="57"/>
+      <c r="Z39" s="57">
+        <v>32.4</v>
+      </c>
       <c r="AA39" s="57"/>
       <c r="AB39" s="57"/>
       <c r="AC39" s="57"/>
@@ -13020,7 +13078,7 @@
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -13038,11 +13096,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.357142857142858</v>
+        <v>31.404545454545453</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.51400974627893703</v>
+        <v>0.56141234368153192</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13122,7 +13180,9 @@
       <c r="Y40" s="57">
         <v>31.3</v>
       </c>
-      <c r="Z40" s="57"/>
+      <c r="Z40" s="57">
+        <v>31.4</v>
+      </c>
       <c r="AA40" s="57"/>
       <c r="AB40" s="57"/>
       <c r="AC40" s="57"/>
@@ -13134,7 +13194,7 @@
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13152,11 +13212,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>29.623809523809523</v>
+        <v>29.704545454545453</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>0.67626113671274268</v>
+        <v>0.75699706744867257</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13236,7 +13296,9 @@
       <c r="Y41" s="57">
         <v>32.6</v>
       </c>
-      <c r="Z41" s="57"/>
+      <c r="Z41" s="57">
+        <v>32</v>
+      </c>
       <c r="AA41" s="57"/>
       <c r="AB41" s="57"/>
       <c r="AC41" s="57"/>
@@ -13248,7 +13310,7 @@
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13266,11 +13328,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.457142857142863</v>
+        <v>30.527272727272734</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>1.0908346134152715</v>
+        <v>1.1609644835451434</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13411,7 +13473,9 @@
       <c r="Y43" s="57">
         <v>33</v>
       </c>
-      <c r="Z43" s="57"/>
+      <c r="Z43" s="57">
+        <v>31.2</v>
+      </c>
       <c r="AA43" s="57"/>
       <c r="AB43" s="57"/>
       <c r="AC43" s="57"/>
@@ -13423,7 +13487,7 @@
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31.2</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -13441,11 +13505,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>30.911111111111111</v>
+        <v>30.926315789473687</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>0.85004928315412087</v>
+        <v>0.86525396151669653</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -13523,7 +13587,9 @@
       <c r="Y44" s="29">
         <v>30.4</v>
       </c>
-      <c r="Z44" s="29"/>
+      <c r="Z44" s="29">
+        <v>31.2</v>
+      </c>
       <c r="AA44" s="29"/>
       <c r="AB44" s="29"/>
       <c r="AC44" s="29"/>
@@ -13535,7 +13601,7 @@
       <c r="AI44" s="57"/>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -13553,11 +13619,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.139999999999993</v>
+        <v>31.142857142857139</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.0968127946395327</v>
+        <v>2.0996699374966781</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -13637,7 +13703,9 @@
       <c r="Y45" s="57">
         <v>31.6</v>
       </c>
-      <c r="Z45" s="57"/>
+      <c r="Z45" s="57">
+        <v>30.4</v>
+      </c>
       <c r="AA45" s="57"/>
       <c r="AB45" s="57"/>
       <c r="AC45" s="57"/>
@@ -13649,7 +13717,7 @@
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -13667,11 +13735,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.371428571428581</v>
+        <v>30.372727272727278</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>0.82561217854975055</v>
+        <v>0.82691087984844813</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -13890,7 +13958,9 @@
       <c r="Y48" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="Z48" s="57"/>
+      <c r="Z48" s="57">
+        <v>32.6</v>
+      </c>
       <c r="AA48" s="57"/>
       <c r="AB48" s="57"/>
       <c r="AC48" s="57"/>
@@ -13902,7 +13972,7 @@
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>32.6</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -13920,11 +13990,11 @@
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.604761904761901</v>
+        <v>30.695454545454542</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.26222904932582125</v>
+        <v>0.35292169001846219</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26823,6 +26893,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -26832,12 +26908,6 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
